--- a/data/trans_bre/P19C05-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P19C05-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 7,31</t>
+          <t>-1,29; 7,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 7,25</t>
+          <t>-1,51; 7,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 5,29</t>
+          <t>-2,48; 5,22</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,55; 6,36</t>
+          <t>0,79; 6,67</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,77; 59,13</t>
+          <t>-7,22; 58,37</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-9,49; 49,64</t>
+          <t>-7,93; 51,11</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-18,65; 64,3</t>
+          <t>-21,66; 63,3</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,23; 70,94</t>
+          <t>6,16; 79,09</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 5,15</t>
+          <t>-2,11; 5,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,94; 8,4</t>
+          <t>1,21; 8,48</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 3,53</t>
+          <t>-3,04; 3,56</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 6,47</t>
+          <t>-1,42; 5,73</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-12,27; 40,82</t>
+          <t>-14,23; 44,43</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,82; 69,15</t>
+          <t>7,33; 71,42</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-23,44; 34,66</t>
+          <t>-23,35; 35,27</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-15,0; 133,95</t>
+          <t>-14,61; 136,15</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 5,95</t>
+          <t>-2,04; 6,35</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 8,4</t>
+          <t>-0,36; 8,4</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 6,12</t>
+          <t>-1,39; 5,87</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,7; 3,29</t>
+          <t>-6,18; 3,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-14,32; 47,31</t>
+          <t>-11,66; 51,22</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 75,2</t>
+          <t>-1,95; 76,54</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-12,16; 95,21</t>
+          <t>-15,94; 89,05</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-59,42; 35,55</t>
+          <t>-55,62; 38,89</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,07; 7,24</t>
+          <t>-0,19; 6,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 5,11</t>
+          <t>-2,11; 5,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 3,77</t>
+          <t>-2,96; 3,45</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 3,91</t>
+          <t>-1,96; 3,93</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 69,4</t>
+          <t>-1,52; 66,71</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-14,18; 36,44</t>
+          <t>-11,77; 36,76</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-22,59; 38,75</t>
+          <t>-22,47; 35,47</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-15,41; 38,96</t>
+          <t>-14,8; 37,78</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,54; 4,66</t>
+          <t>0,56; 4,36</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,31; 5,12</t>
+          <t>1,11; 5,31</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 2,85</t>
+          <t>-0,69; 2,71</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 3,67</t>
+          <t>-0,51; 4,06</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,4; 36,38</t>
+          <t>3,47; 34,08</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,77; 36,56</t>
+          <t>6,88; 38,05</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,61; 29,42</t>
+          <t>-6,01; 27,68</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-7,36; 45,11</t>
+          <t>-4,27; 50,58</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P19C05-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P19C05-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,64</t>
+          <t>3,55</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>34,96%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 7,23</t>
+          <t>-1,85; 7,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 7,43</t>
+          <t>-1,3; 7,48</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 5,22</t>
+          <t>-2,27; 5,61</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,79; 6,67</t>
+          <t>0,55; 6,24</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,22; 58,37</t>
+          <t>-10,85; 57,12</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,93; 51,11</t>
+          <t>-6,95; 51,2</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-21,66; 63,3</t>
+          <t>-19,44; 63,73</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,16; 79,09</t>
+          <t>4,53; 74,35</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,61</t>
+          <t>-0,19</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>-2,04%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 5,34</t>
+          <t>-2,07; 5,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,21; 8,48</t>
+          <t>1,05; 8,19</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 3,56</t>
+          <t>-3,14; 3,41</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 5,73</t>
+          <t>-2,63; 1,94</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-14,23; 44,43</t>
+          <t>-13,59; 45,07</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,33; 71,42</t>
+          <t>6,48; 68,12</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-23,35; 35,27</t>
+          <t>-22,95; 32,83</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-14,61; 136,15</t>
+          <t>-23,63; 24,09</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,55</t>
+          <t>1,92</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-5,66%</t>
+          <t>18,46%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 6,35</t>
+          <t>-2,07; 6,92</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 8,4</t>
+          <t>-0,32; 8,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 5,87</t>
+          <t>-1,36; 5,79</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,18; 3,47</t>
+          <t>-1,06; 4,76</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-11,66; 51,22</t>
+          <t>-10,92; 57,4</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 76,54</t>
+          <t>-3,15; 80,18</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-15,94; 89,05</t>
+          <t>-13,36; 91,75</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-55,62; 38,89</t>
+          <t>-8,67; 55,05</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,26</t>
+          <t>2,04</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>17,53%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 6,96</t>
+          <t>-0,03; 6,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 5,18</t>
+          <t>-2,47; 4,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 3,45</t>
+          <t>-2,52; 4,02</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 3,93</t>
+          <t>-0,3; 4,76</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 66,71</t>
+          <t>-0,18; 69,16</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-11,77; 36,76</t>
+          <t>-13,3; 32,48</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-22,47; 35,47</t>
+          <t>-19,42; 41,43</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-14,8; 37,78</t>
+          <t>-2,25; 47,99</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,56</t>
+          <t>1,7</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,38%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,56; 4,36</t>
+          <t>0,46; 4,38</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,11; 5,31</t>
+          <t>1,16; 5,11</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 2,71</t>
+          <t>-0,8; 2,75</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 4,06</t>
+          <t>0,52; 3,18</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,47; 34,08</t>
+          <t>3,27; 35,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,88; 38,05</t>
+          <t>7,72; 37,39</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-6,01; 27,68</t>
+          <t>-7,01; 28,16</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 50,58</t>
+          <t>4,74; 33,49</t>
         </is>
       </c>
     </row>
